--- a/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="1095">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>006</t>
   </si>
   <si>
-    <t>Andrologie</t>
+    <t>Andrologie (urologie médicale)</t>
   </si>
   <si>
     <t>007</t>
@@ -744,7 +744,7 @@
     <t>152</t>
   </si>
   <si>
-    <t>Urgences spécialisées Médico-Judiciaires (UMJ)</t>
+    <t>Evaluation Médico-Judiciaires (UMJ)</t>
   </si>
   <si>
     <t>154</t>
@@ -768,7 +768,7 @@
     <t>158</t>
   </si>
   <si>
-    <t>Urgences spécialisées psychiatriques</t>
+    <t>Urgences psychiatriques</t>
   </si>
   <si>
     <t>159</t>
@@ -1608,7 +1608,7 @@
     <t>309</t>
   </si>
   <si>
-    <t>Accompagnements à la vie affective et sexuelle</t>
+    <t>Accompagnements à la vie intime, affective et sexuelle</t>
   </si>
   <si>
     <t>310</t>
@@ -2370,7 +2370,7 @@
     <t>448</t>
   </si>
   <si>
-    <t>Diagnostic lié à un retard ou trouble du développement</t>
+    <t>Diagnostic lié à un retard ou Trouble du Neuro-Développement (TND)</t>
   </si>
   <si>
     <t>449</t>
@@ -2682,7 +2682,7 @@
     <t>510</t>
   </si>
   <si>
-    <t>Échographie obstétricale</t>
+    <t>Échographie obstétricale de dépistage (1er, 2ème, 3ème trimestre)</t>
   </si>
   <si>
     <t>511</t>
@@ -3225,10 +3225,70 @@
     <t>Médiation pour le maintien en hospitalisation</t>
   </si>
   <si>
+    <t>602</t>
+  </si>
+  <si>
+    <t>Pair aidance pour l'autodétermination</t>
+  </si>
+  <si>
     <t>603</t>
   </si>
   <si>
     <t>Prise en charge coordonnée des patients atteints de maladies neurodégénératives</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée orthopédique</t>
+  </si>
+  <si>
+    <t>605</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée digestif et viscérale</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Accompagnement pour l’autodétermination de la personne</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du secteur sanitaire</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du milieu ordinaire</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès de acteurs du secteur judiciaire</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Pédiatrie spécialisée pneumologie</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Psychiatrie de crise</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Echographie obstétricale de diagnostic</t>
   </si>
   <si>
     <t/>
@@ -3499,7 +3559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7695,15 +7755,95 @@
         <v>1072</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="B526" t="s" s="2">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="B527" t="s" s="2">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="B528" t="s" s="2">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="B529" t="s" s="2">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="B530" t="s" s="2">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="B531" t="s" s="2">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="s" s="2">
+        <v>1088</v>
+      </c>
+      <c r="B532" t="s" s="2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="s" s="2">
+        <v>1090</v>
+      </c>
+      <c r="B533" t="s" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="s" s="2">
+        <v>1092</v>
+      </c>
+      <c r="B534" t="s" s="2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="B535" t="s" s="2">
+        <v>1094</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="1097">
   <si>
     <t>Property</t>
   </si>
@@ -3276,16 +3276,22 @@
     <t>610</t>
   </si>
   <si>
+    <t>Pédiatrie spécialisée neurologie</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
     <t>Pédiatrie spécialisée pneumologie</t>
   </si>
   <si>
-    <t>611</t>
+    <t>612</t>
   </si>
   <si>
     <t>Psychiatrie de crise</t>
   </si>
   <si>
-    <t>612</t>
+    <t>613</t>
   </si>
   <si>
     <t>Echographie obstétricale de diagnostic</t>
@@ -3559,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7835,15 +7841,23 @@
         <v>1092</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>1094</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="B536" t="s" s="2">
+        <v>1096</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="1105">
   <si>
     <t>Property</t>
   </si>
@@ -3295,6 +3295,30 @@
   </si>
   <si>
     <t>Echographie obstétricale de diagnostic</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en pathologies chroniques stabilisées</t>
+  </si>
+  <si>
+    <t>615</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en oncologie et hémato-oncologie</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en maladie rénale chronique</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en santé mentale</t>
   </si>
   <si>
     <t/>
@@ -3565,7 +3589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7849,15 +7873,47 @@
         <v>1094</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="B537" t="s" s="2">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B538" t="s" s="2">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="s" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B539" t="s" s="2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B540" t="s" s="2">
+        <v>1104</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -744,7 +744,7 @@
     <t>152</t>
   </si>
   <si>
-    <t>Evaluation Médico-Judiciaires (UMJ)</t>
+    <t>Evaluation Médico-Judiciaire (UMJ)</t>
   </si>
   <si>
     <t>154</t>
